--- a/docs/데이터관리_데모용.xlsx
+++ b/docs/데이터관리_데모용.xlsx
@@ -2,9 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="데모시나리오" sheetId="1" state="visible" r:id="rId1"/>
@@ -20,24 +19,43 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'보류'!$A$1:$C$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'포털주소'!$A$1:$B$5</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <charset val="129"/>
+      <family val="3"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -49,7 +67,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
   </fills>
@@ -63,23 +81,25 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00BFBFBF"/>
+        <color rgb="FFBFBFBF"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -88,50 +108,54 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="6">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00C6EFCE"/>
+          <fgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFEB9C"/>
+          <fgColor rgb="FFE4DFEC"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00F2F2F2"/>
+          <fgColor rgb="FFDDEBF7"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00DDEBF7"/>
+          <fgColor rgb="FFF2F2F2"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00E4DFEC"/>
+          <fgColor rgb="FFFFEB9C"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor rgb="00FFC7CE"/>
+          <fgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -498,7 +522,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
@@ -528,7 +552,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="34" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
@@ -548,7 +572,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="34" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -568,7 +592,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -601,7 +625,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
@@ -724,21 +748,21 @@
           <t>가상생성</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>파일</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
           <t>가상매출 시트 참고</t>
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="34" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -749,7 +773,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>대구 과거 날씨(일자료)</t>
+          <t>대구 과거 날씨 (ASOS 일자료)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -769,23 +793,31 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>대구 관측소(143), 2023~2025 일 강수량·기온</t>
+          <t>대구 관측소(143), 2023-01-01~2026-09-13, 평균·최저·최고기온, 일강수량</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>미확인</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>확보</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="n"/>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>파일(CSV)</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr"/>
-      <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/weather/, cp949. 강수 빈칸=비 안 옴, 0=흔적. 2024-02-21 최고기온 1건 결측</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -826,21 +858,21 @@
           <t>미확인</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>API</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr"/>
-      <c r="L4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>API 안 되면 예보값 고정해서 시연</t>
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="68" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -871,17 +903,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>개최일, 장소(주소·좌표) 유무</t>
+          <t>개최기간·장소(텍스트, 좌표 없음)</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>목록확인</t>
+          <t>확보</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15013104 (대구광역시_문화축제)</t>
+          <t>15130238 (대구광역시_문화축제_20241231)</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -889,15 +921,19 @@
           <t>파일</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="n"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>좌표 없으면 행정동만 수기 입력</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
+          <t>2024년 32건만 제공. 장소→행정동 수기 매칭, 2023·2025는 매년 열리는 축제 날짜 이동으로 대체. data/raw/festival/</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -933,24 +969,28 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>코드로처리</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>확보</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n"/>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="n"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>API 대신 목록 하드코딩</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
+          <t>data/holidays_kr.csv (대체·임시·선거일 포함)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -999,15 +1039,15 @@
           <t>API</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="n"/>
+      <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
           <t>KAMIS에 축산물 소매가 포함</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="51" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -1056,7 +1096,7 @@
           <t>파일</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>2026-09-13</t>
@@ -1068,7 +1108,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="34" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -1117,33 +1157,37 @@
           <t>파일</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="n"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr"/>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>data/raw/boundary/ 재다운로드 완료</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M9"/>
   <conditionalFormatting sqref="H2:H500">
-    <cfRule type="expression" priority="1" dxfId="0">
+    <cfRule type="expression" priority="1" dxfId="5">
       <formula>$H2="확보"</formula>
     </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
+    <cfRule type="expression" priority="2" dxfId="4">
       <formula>$H2="목록확인"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
+    <cfRule type="expression" priority="3" dxfId="3">
       <formula>$H2="미확인"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="3">
+    <cfRule type="expression" priority="4" dxfId="2">
       <formula>$H2="가상생성"</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
+    <cfRule type="expression" priority="5" dxfId="1">
       <formula>$H2="코드로처리"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="5">
+    <cfRule type="expression" priority="6" dxfId="0">
       <formula>$H2="제외"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1163,7 +1207,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -1442,7 +1486,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
@@ -1632,7 +1675,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
@@ -1673,7 +1716,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="34" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>행사</t>
@@ -1690,7 +1733,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="34" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>식자재</t>
@@ -1805,7 +1848,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
@@ -1853,7 +1896,7 @@
           <t>D-데이터허브(대구)</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>https://data.daegu.go.kr</t>
         </is>
@@ -1873,6 +1916,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:B5"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B4" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>